--- a/src/test/output_test/ID_with_problems.xlsx
+++ b/src/test/output_test/ID_with_problems.xlsx
@@ -22,7 +22,7 @@
     <t>Errore</t>
   </si>
   <si>
-    <t>cannot unpack non-iterable NoneType object</t>
+    <t>You knew there was an error</t>
   </si>
 </sst>
 </file>
